--- a/data/nzd0556/nzd0556.xlsx
+++ b/data/nzd0556/nzd0556.xlsx
@@ -14772,7 +14772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17675,6 +17675,16 @@
       </c>
       <c r="B290" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
